--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-29T07:23:21+00:00</t>
+    <t>2024-07-01T07:47:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T07:47:51+00:00</t>
+    <t>2024-07-01T18:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T18:04:04+00:00</t>
+    <t>2024-07-01T19:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:43:16+00:00</t>
+    <t>2024-07-01T19:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:47:03+00:00</t>
+    <t>2024-07-08T21:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T21:31:51+00:00</t>
+    <t>2024-07-13T00:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T00:07:23+00:00</t>
+    <t>2024-07-22T01:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T01:54:40+00:00</t>
+    <t>2024-08-18T18:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T18:57:20+00:00</t>
+    <t>2024-08-18T19:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T19:14:17+00:00</t>
+    <t>2024-10-17T13:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T13:36:11+00:00</t>
+    <t>2024-10-30T19:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T19:02:49+00:00</t>
+    <t>2024-11-07T20:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T20:59:16+00:00</t>
+    <t>2024-12-06T22:28:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T22:28:12+00:00</t>
+    <t>2024-12-30T06:20:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T06:20:40+00:00</t>
+    <t>2025-01-13T15:35:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T15:35:56+00:00</t>
+    <t>2025-01-13T20:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:12:32+00:00</t>
+    <t>2025-01-30T04:55:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T04:55:08+00:00</t>
+    <t>2025-01-31T22:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T22:08:22+00:00</t>
+    <t>2025-02-01T06:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T06:47:49+00:00</t>
+    <t>2025-02-01T23:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:07:45+00:00</t>
+    <t>2025-02-01T23:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.4.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:40:00+00:00</t>
+    <t>2025-02-02T03:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE491.xlsx
+++ b/ValueSet-HIV.D.DE491.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-10T17:41:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
